--- a/backend/storage/output/excel/types/Rail_Madad_Report_4_Cause_Wise_Top_10_Trains_13-07-2026.xlsx
+++ b/backend/storage/output/excel/types/Rail_Madad_Report_4_Cause_Wise_Top_10_Trains_13-07-2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,21 +36,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <color rgb="00000000"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -71,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -82,8 +74,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,27 +496,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CSMT-NGP SEWAGRAM EXP [SUPERFAST]</t>
+          <t>DADN-PRYJ EXP. [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>North Central Railway</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>NAGPUR DIVISION</t>
+          <t>PRAYAGRAJ DIVISION</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -538,27 +528,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CSMT-G VIDARBHA EXP [SUPERFAST]</t>
+          <t>MFP-SMVB EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -570,57 +560,57 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>G-CSMT VIDARBHA EXP [SUPERFAST]</t>
+          <t>HWH NDLS POORVA EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>Eastern Railway</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>HOWRAH DIVISION</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>G-KOP MAHARASHTRA EXP [MAIL EXPRESS]</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>Central Railway</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>BOMBAY DIVISION</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>12106</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>DNR-SC EXP [SUPERFAST]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>South Central Railway</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>SECUNDERABAD DIVISION</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>12792</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PUNE DIVISION</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -634,7 +624,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PUNE HWH AZAD HIND EXP [SUPERFAST]</t>
+          <t>G-CSMT VIDARBHA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -644,17 +634,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>PUNE DIVISION</t>
+          <t>BOMBAY DIVISION</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -666,27 +656,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>KOAA - ADI EXPRESS [MAIL EXPRESS]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>AHMEDABAD DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -698,27 +688,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>GODA - LT(T) WKLY EXP [SUPERFAST]</t>
+          <t>NZM-JBP MAHAKOSHAL EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Eastern Railway</t>
+          <t>West Central Railway</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MALDA DIVISION</t>
+          <t>JABALPUR DIVISION</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -730,27 +720,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>DOZ-GODA EXPRESS [MAIL EXPRESS]</t>
+          <t>BGP ANVT VIKRAM SHILA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>North Western Railway</t>
+          <t>Eastern Railway</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>AJMER DIVISION</t>
+          <t>MALDA DIVISION</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -762,27 +752,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CSMT-NGP DURONTO [DURONTO EXPRESS]</t>
+          <t>DNR-SMVB SANGHAMITRA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>South Western Railway</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>BANGALORE DIVISION</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -794,27 +784,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>MALWA EXPRESS [SUPERFAST]</t>
+          <t>NDLS-SBC KARNATAKA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>South Western Railway</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>RATLAM DIVISION</t>
+          <t>BANGALORE DIVISION</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -865,27 +855,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>KOAA - ADI EXPRESS [MAIL EXPRESS]</t>
+          <t>GARIB RATH EX [GARIB RATH]</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>AHMEDABAD DIVISION</t>
+          <t>FIROZPUR DIVISION</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -897,27 +887,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>OKHA-GHY DWARKA EXPRESS [MAIL EXPRESS]</t>
+          <t>JAT - SBIB EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Western Railway</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>AHMEDABAD DIVISION</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -929,7 +919,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ASR-KIR EXPRESS [MAIL EXPRESS]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -939,17 +929,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>KATIHAR DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -961,7 +951,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -976,12 +966,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -993,7 +983,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SHC GARIB RATH [GARIB RATH]</t>
+          <t>HUMSAFAR EXP SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1008,12 +998,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>04651</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1025,27 +1015,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
+          <t>CSMT HWH GITANJALI EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>South Eastern Railway</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>KHARAGPUR DIVISION</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1047,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HUMSAFAR EXPRESS [SUPERFAST]</t>
+          <t>ASR-KIR EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1067,12 +1057,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>KATIHAR DIVISION</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1089,27 +1079,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SABARMATI EXP [MAIL EXPRESS]</t>
+          <t>JAT-PUNE JHELUM EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>AHMEDABAD DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1111,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>NTSK-SMVB S/F EXPRESS [SUPERFAST]</t>
+          <t>FZR-CSMT PUNJAB MAIL [SUPERFAST]</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>BOMBAY DIVISION</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1153,27 +1143,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>VIVEK EXPRESS [SUPERFAST]</t>
+          <t>SMVB-DNR SANGHAMITRA EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>South Western Railway</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>BANGALORE DIVISION</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1224,22 +1214,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>HUMSAFAR EXPRESS [SUPERFAST]</t>
+          <t>NGP-CSMT SEWAGRAM EXP. [SUPERFAST]</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>NAGPUR DIVISION</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1256,22 +1246,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>AMH-BDTS SF SPL TOD [TRAIN ON DEMAND]</t>
+          <t>JAT-PUNE JHELUM EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>VARANASI DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>05183</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1288,22 +1278,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>HWH JAT HIMGIRI EXPRESS [MAIL EXPRESS]</t>
+          <t>CDG - LKO EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Eastern Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>HOWRAH DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1352,22 +1342,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DNR-SMVB SANGHAMITRA EXP [SUPERFAST]</t>
+          <t>PUNE HWH AZAD HIND EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>South Western Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>BANGALORE DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1384,22 +1374,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>GAYA-CHENNAI EXPRESS [SUPERFAST]</t>
+          <t>KGM GARIBRATH- [GARIB RATH]</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>East Central Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Pt. DEEN DAYAL UPADHYAYA DIVISION</t>
+          <t>JAMMU DIVISION</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1416,22 +1406,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>KRISHAK EXPRESS [MAIL EXPRESS]</t>
+          <t>VIVEK EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>LUCKNOW DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1448,7 +1438,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>VIVEK EXPRESS [SUPERFAST]</t>
+          <t>KOAA-DBRG TOD SPECIAL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1463,12 +1453,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>05931</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1470,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>G-KOP MAHARASHTRA EXP [MAIL EXPRESS]</t>
+          <t>DHN-KOP DIKSHABHUMI EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1495,7 +1485,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1512,7 +1502,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>JAT-PUNE JHELUM EXPRESS [MAIL EXPRESS]</t>
+          <t>SOU-PUNE EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1527,7 +1517,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1583,27 +1573,27 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>PRYJ-UBL SUMMER SPL [TRAIN ON DEMAND]</t>
+          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>North Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>PRAYAGRAJ DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>04113</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1615,27 +1605,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>AVADH EXPRESS [MAIL EXPRESS]</t>
+          <t>YPR- SHC SPECIAL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>MUMBAI DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>05552</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1647,27 +1637,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>KARMABHOOMI EXPRESS [SUPERFAST]</t>
+          <t>MAURYA EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>North Eastern Railway</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1679,27 +1669,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>HUMSAFAR EXPRESS [SUPERFAST]</t>
+          <t>PRYJ-UDN SUMMER SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>North Central Railway</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>PRAYAGRAJ DIVISION</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>04105</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1711,27 +1701,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>GHY-BKN EXPRESS [MAIL EXPRESS]</t>
+          <t>PRNC-ANVT EXPRESS SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>05579</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1743,27 +1733,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>BRAHMAPUTRA MAIL [MAIL EXPRESS]</t>
+          <t>MBI - UDN SPECIAL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Western Railway</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>MUMBAI DIVISION</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>09152</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1765,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GHY-LEDO I/C EXPRESS [MAIL EXPRESS]</t>
+          <t>GARIB RATH EX [GARIB RATH]</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>FIROZPUR DIVISION</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -1807,27 +1797,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>AMARNATH EXPRESS [MAIL EXPRESS]</t>
+          <t>YPR-BBS SUMMER SPECIAL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>East Coast Railway</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>KHURDA DIVISION</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>02812</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1839,22 +1829,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>JBP-CBE SF SPL [TRAIN ON DEMAND]</t>
+          <t>HUMSAFAR EXP SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>West Central Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>JABALPUR DIVISION</t>
+          <t>FIROZPUR DIVISION</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>02198</t>
+          <t>04651</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -1871,22 +1861,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>SMVB-GWL EXP [MAIL EXPRESS]</t>
+          <t>KYQ-SVDK EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>North Central Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>JHANSI DIVISION</t>
+          <t>LUMDING DIVISION</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -1942,27 +1932,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>MAU-ANVT EXPRESS [MAIL EXPRESS]</t>
+          <t>NZM-MAS GARIBRATH [GARIB RATH]</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>VARANASI DIVISION</t>
+          <t>CHENNAI DIVISION</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1974,27 +1964,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>MMCT-KIR SPECIAL [TRAIN ON DEMAND]</t>
+          <t>BBS-HWH JAN SHATABDI [JAN SHATABDI]</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>East Coast Railway</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>MUMBAI DIVISION</t>
+          <t>KHURDA DIVISION</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>09189</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -2006,27 +1996,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>LJN- GKP INTERCITY EXP. [MAIL EXPRESS]</t>
+          <t>BUI-DR SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>LUCKNOW DIVISION</t>
+          <t>BOMBAY DIVISION</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>01026</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2038,27 +2028,27 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>DNR-HDP SPL [TRAIN ON DEMAND]</t>
+          <t>YNRK-MFP SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>PUNE DIVISION</t>
+          <t>MORADABAD DIVISION</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>01450</t>
+          <t>04314</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2070,27 +2060,27 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>LKQ-ANVT SPL [TRAIN ON DEMAND]</t>
+          <t>MAS- SBC DOUBLE DECKER [SUPERFAST]</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>DELHI DIVISION</t>
+          <t>CHENNAI DIVISION</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>04013</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2102,22 +2092,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>BANDRA - BHUJ SPECIAL [TRAIN ON DEMAND]</t>
+          <t>DNR-HDP SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Western Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>MUMBAI DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>09009</t>
+          <t>01450</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2134,7 +2124,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SHC GARIB RATH [GARIB RATH]</t>
+          <t>ASR-BJU SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2149,7 +2139,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>04610</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2166,27 +2156,27 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>PRYJ-UBL SUMMER SPL [TRAIN ON DEMAND]</t>
+          <t>BBU-PNBE INTERCITY EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>North Central Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>PRAYAGRAJ DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>04113</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2198,22 +2188,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>AYC-ANVT SPL [TRAIN ON DEMAND]</t>
+          <t>PUNE-SOU EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>LUCKNOW DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>04213</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2230,22 +2220,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>YNRK-MFP SPL [TRAIN ON DEMAND]</t>
+          <t>HWH-CSMT MAIL [SUPERFAST]</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>South Eastern Railway</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>MORADABAD DIVISION</t>
+          <t>KHARAGPUR DIVISION</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>04314</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2301,22 +2291,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>SGRL-NZM URJADHANI SF EXP [SUPERFAST]</t>
+          <t>SNSI-PURI WEEKLY EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>West Central Railway</t>
+          <t>East Coast Railway</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>BHOPAL DIVISION</t>
+          <t>KHURDA DIVISION</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2333,22 +2323,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>YPR-DEE DURONTO EXP [DURONTO EXPRESS]</t>
+          <t>PUNE HWH AZAD HIND EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>South Western Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>BANGALORE DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2365,27 +2355,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>HWH-SMVB DURONTO EXPRESS [DURONTO EXPRESS]</t>
+          <t>GKP- YPR SF [SUPERFAST]</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>South Eastern Railway</t>
+          <t>North Eastern Railway</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>KHARAGPUR DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2397,27 +2387,27 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>NZM-ERS MANGALA SF EXP [SUPERFAST]</t>
+          <t>PNBE-NDLS EXPRESS SPL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Southern Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>THIRUVANANTHAPURAM DIVISION</t>
+          <t>DANAPUR DIVISION</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>03293</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2429,27 +2419,27 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>BNRS-ANVT GARIBRATH EXP. [GARIB RATH]</t>
+          <t>PPTA-LTT SF EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>VARANASI DIVISION</t>
+          <t>BOMBAY DIVISION</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2451,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HWH-PUNE DURONTO EXPRESS [DURONTO EXPRESS]</t>
+          <t>PUNE DURANTO EXP [DURONTO EXPRESS]</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>South Eastern Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>KHARAGPUR DIVISION</t>
+          <t>DELHI DIVISION</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2493,22 +2483,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>BME-HWH BI WKLY EXP [SUPERFAST]</t>
+          <t>DURONTO EXPRESS [DURONTO EXPRESS]</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Eastern Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>HOWRAH DIVISION</t>
+          <t>DELHI DIVISION</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -2525,22 +2515,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>ASR SDAH JALIANWALABAGH E [SUPERFAST]</t>
+          <t>SADBHAWANA EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Eastern Railway</t>
+          <t>Northern Railway</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>SEALDAH DIVISION</t>
+          <t>DELHI DIVISION</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -2557,22 +2547,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>NZM SC RAJDHANI EXPRESS [RAJDHANI]</t>
+          <t>ANVT-RXL SATYAGRAH EXP [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>DELHI DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -2582,32 +2572,32 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>HYB-NDLSTELANGANA EXPRESS [SUPERFAST]</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>South Central Railway</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>SECUNDERABAD DIVISION</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>12723</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>BRAHMAPUTRA MAIL [MAIL EXPRESS]</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Northeast Frontier Railway</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>LUMDING DIVISION</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>15658</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2660,27 +2650,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
+          <t>JAT-PNBE ARCHANA EXPRESS [SUPERFAST]</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>TINSUKIA DIVISION</t>
+          <t>DANAPUR DIVISION</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2692,27 +2682,27 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>GKP-BNRS INTERCITY EXP [MAIL EXPRESS]</t>
+          <t>AVADH ASSAM EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>North Eastern Railway</t>
+          <t>Northeast Frontier Railway</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>LUCKNOW DIVISION</t>
+          <t>TINSUKIA DIVISION</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2714,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>OKHA-GHY DWARKA EXPRESS [MAIL EXPRESS]</t>
+          <t>KYQ-PURI EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2739,12 +2729,12 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2761,12 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2788,22 +2778,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NDLS-DBG SPECIAL [TRAIN ON DEMAND]</t>
+          <t>JBN-ED AMRIT BHARAT EXP [AMRIT BHARAT]</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>East Central Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>SAMASTIPUR DIVISION</t>
+          <t>SALEM DIVISION</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>02570</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -2820,27 +2810,27 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>NJP-ASR AMTB SPL [AMRIT BHARAT]</t>
+          <t>PUSHPAK SF EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Northern Railway</t>
+          <t>North Eastern Railway</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>FIROZPUR DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2852,22 +2842,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GKP-CSMT SPL [TRAIN ON DEMAND]</t>
+          <t>MAS-ADI NAVJEEVAN SF EXP [SUPERFAST]</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Central Railway</t>
+          <t>Southern Railway</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>BOMBAY DIVISION</t>
+          <t>CHENNAI DIVISION</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>01080</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -2884,22 +2874,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>NORTHEAST EXPRESS [SUPERFAST]</t>
+          <t>KUSHINAGAR SF [SUPERFAST]</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Northeast Frontier Railway</t>
+          <t>North Eastern Railway</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>LUMDING DIVISION</t>
+          <t>LUCKNOW DIVISION</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -2916,27 +2906,27 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>AII SDAH EXP [SUPERFAST]</t>
+          <t>DBG-NDLS SPECIAL [TRAIN ON DEMAND]</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>North Western Railway</t>
+          <t>East Central Railway</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>AJMER DIVISION</t>
+          <t>SAMASTIPUR DIVISION</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>02569</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2948,27 +2938,27 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>RGD-LTT EXPRESS [MAIL EXPRESS]</t>
+          <t>PUNE-SOU EXPRESS [MAIL EXPRESS]</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>East Central Railway</t>
+          <t>Central Railway</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>DANAPUR DIVISION</t>
+          <t>PUNE DIVISION</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
